--- a/file_excel/fake_data.xlsx
+++ b/file_excel/fake_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Chanh Resources\Intern\workspace\UMinhThuong-BioDB\file_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91C5C364-8683-4312-B4B8-F015EC8D225C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDA8F7DB-252F-4F7C-A7A9-9E5D560FAE3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3972" yWindow="2448" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5912" uniqueCount="2055">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6012" uniqueCount="2055">
   <si>
     <t>Dự án 49</t>
   </si>
@@ -6937,7 +6937,7 @@
         <v>244</v>
       </c>
       <c r="G2" s="4">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="H2" s="4">
         <v>40</v>
@@ -6994,7 +6994,7 @@
         <v>2264</v>
       </c>
       <c r="Z2" s="4">
-        <v>500</v>
+        <v>330</v>
       </c>
       <c r="AA2" s="4" t="s">
         <v>742</v>
@@ -7005,8 +7005,8 @@
       <c r="AC2" s="4">
         <v>83.226614999999995</v>
       </c>
-      <c r="AD2" s="4" t="b">
-        <v>1</v>
+      <c r="AD2" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE2" s="4" t="s">
         <v>743</v>
@@ -7021,13 +7021,13 @@
         <v>1</v>
       </c>
       <c r="AI2" s="4">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AJ2" s="4">
-        <v>9</v>
+        <v>2000</v>
       </c>
       <c r="AK2" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL2" s="4" t="s">
         <v>850</v>
@@ -7186,7 +7186,7 @@
         <v>245</v>
       </c>
       <c r="G3" s="4">
-        <v>674</v>
+        <v>1101</v>
       </c>
       <c r="H3" s="4">
         <v>64</v>
@@ -7254,8 +7254,8 @@
       <c r="AC3" s="4">
         <v>17.036134000000001</v>
       </c>
-      <c r="AD3" s="4" t="b">
-        <v>0</v>
+      <c r="AD3" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE3" s="4" t="s">
         <v>743</v>
@@ -7270,10 +7270,10 @@
         <v>1</v>
       </c>
       <c r="AI3" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ3" s="4">
-        <v>5</v>
+        <v>2000</v>
       </c>
       <c r="AK3" s="4" t="b">
         <v>1</v>
@@ -7503,8 +7503,8 @@
       <c r="AC4" s="4">
         <v>-65.071988000000005</v>
       </c>
-      <c r="AD4" s="4" t="b">
-        <v>1</v>
+      <c r="AD4" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE4" s="4" t="s">
         <v>744</v>
@@ -7516,13 +7516,13 @@
         <v>808</v>
       </c>
       <c r="AH4" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AI4" s="4">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="AJ4" s="4">
-        <v>10</v>
+        <v>2000</v>
       </c>
       <c r="AK4" s="4" t="b">
         <v>1</v>
@@ -7752,8 +7752,8 @@
       <c r="AC5" s="4">
         <v>74.154150000000001</v>
       </c>
-      <c r="AD5" s="4" t="b">
-        <v>0</v>
+      <c r="AD5" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE5" s="4" t="s">
         <v>744</v>
@@ -7768,10 +7768,10 @@
         <v>1</v>
       </c>
       <c r="AI5" s="4">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="AJ5" s="4">
-        <v>9</v>
+        <v>2000</v>
       </c>
       <c r="AK5" s="4" t="b">
         <v>1</v>
@@ -8001,8 +8001,8 @@
       <c r="AC6" s="4">
         <v>47.316079999999999</v>
       </c>
-      <c r="AD6" s="4" t="b">
-        <v>1</v>
+      <c r="AD6" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE6" s="4" t="s">
         <v>744</v>
@@ -8017,10 +8017,10 @@
         <v>1</v>
       </c>
       <c r="AI6" s="4">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="AJ6" s="4">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="AK6" s="4" t="b">
         <v>1</v>
@@ -8250,8 +8250,8 @@
       <c r="AC7" s="4">
         <v>87.647735999999995</v>
       </c>
-      <c r="AD7" s="4" t="b">
-        <v>1</v>
+      <c r="AD7" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE7" s="4" t="s">
         <v>744</v>
@@ -8266,10 +8266,10 @@
         <v>1</v>
       </c>
       <c r="AI7" s="4">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AJ7" s="4">
-        <v>12</v>
+        <v>2000</v>
       </c>
       <c r="AK7" s="4" t="b">
         <v>1</v>
@@ -8499,8 +8499,8 @@
       <c r="AC8" s="4">
         <v>-78.064193000000003</v>
       </c>
-      <c r="AD8" s="4" t="b">
-        <v>0</v>
+      <c r="AD8" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE8" s="4" t="s">
         <v>743</v>
@@ -8515,10 +8515,10 @@
         <v>1</v>
       </c>
       <c r="AI8" s="4">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="AJ8" s="4">
-        <v>6</v>
+        <v>2000</v>
       </c>
       <c r="AK8" s="4" t="b">
         <v>1</v>
@@ -8748,8 +8748,8 @@
       <c r="AC9" s="4">
         <v>17.288149000000001</v>
       </c>
-      <c r="AD9" s="4" t="b">
-        <v>1</v>
+      <c r="AD9" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE9" s="4" t="s">
         <v>744</v>
@@ -8764,10 +8764,10 @@
         <v>1</v>
       </c>
       <c r="AI9" s="4">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="AJ9" s="4">
-        <v>5</v>
+        <v>2000</v>
       </c>
       <c r="AK9" s="4" t="b">
         <v>1</v>
@@ -8997,8 +8997,8 @@
       <c r="AC10" s="4">
         <v>-65.622719000000004</v>
       </c>
-      <c r="AD10" s="4" t="b">
-        <v>1</v>
+      <c r="AD10" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE10" s="4" t="s">
         <v>744</v>
@@ -9013,10 +9013,10 @@
         <v>1</v>
       </c>
       <c r="AI10" s="4">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="AJ10" s="4">
-        <v>6</v>
+        <v>2000</v>
       </c>
       <c r="AK10" s="4" t="b">
         <v>1</v>
@@ -9246,8 +9246,8 @@
       <c r="AC11" s="4">
         <v>77.347549999999998</v>
       </c>
-      <c r="AD11" s="4" t="b">
-        <v>1</v>
+      <c r="AD11" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE11" s="4" t="s">
         <v>743</v>
@@ -9262,10 +9262,10 @@
         <v>1</v>
       </c>
       <c r="AI11" s="4">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AJ11" s="4">
-        <v>2</v>
+        <v>2000</v>
       </c>
       <c r="AK11" s="4" t="b">
         <v>1</v>
@@ -9495,8 +9495,8 @@
       <c r="AC12" s="4">
         <v>33.834052999999997</v>
       </c>
-      <c r="AD12" s="4" t="b">
-        <v>1</v>
+      <c r="AD12" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE12" s="4" t="s">
         <v>744</v>
@@ -9511,10 +9511,10 @@
         <v>1</v>
       </c>
       <c r="AI12" s="4">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="AJ12" s="4">
-        <v>8</v>
+        <v>2000</v>
       </c>
       <c r="AK12" s="4" t="b">
         <v>1</v>
@@ -9744,8 +9744,8 @@
       <c r="AC13" s="4">
         <v>41.524588000000001</v>
       </c>
-      <c r="AD13" s="4" t="b">
-        <v>0</v>
+      <c r="AD13" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE13" s="4" t="s">
         <v>743</v>
@@ -9760,10 +9760,10 @@
         <v>1</v>
       </c>
       <c r="AI13" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AJ13" s="4">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="AK13" s="4" t="b">
         <v>1</v>
@@ -9993,8 +9993,8 @@
       <c r="AC14" s="4">
         <v>80.616624000000002</v>
       </c>
-      <c r="AD14" s="4" t="b">
-        <v>0</v>
+      <c r="AD14" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE14" s="4" t="s">
         <v>743</v>
@@ -10009,10 +10009,10 @@
         <v>1</v>
       </c>
       <c r="AI14" s="4">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="AJ14" s="4">
-        <v>12</v>
+        <v>2000</v>
       </c>
       <c r="AK14" s="4" t="b">
         <v>1</v>
@@ -10242,8 +10242,8 @@
       <c r="AC15" s="4">
         <v>25.772967000000001</v>
       </c>
-      <c r="AD15" s="4" t="b">
-        <v>1</v>
+      <c r="AD15" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE15" s="4" t="s">
         <v>744</v>
@@ -10258,10 +10258,10 @@
         <v>1</v>
       </c>
       <c r="AI15" s="4">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="AJ15" s="4">
-        <v>7</v>
+        <v>2000</v>
       </c>
       <c r="AK15" s="4" t="b">
         <v>1</v>
@@ -10491,8 +10491,8 @@
       <c r="AC16" s="4">
         <v>53.612042000000002</v>
       </c>
-      <c r="AD16" s="4" t="b">
-        <v>1</v>
+      <c r="AD16" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE16" s="4" t="s">
         <v>744</v>
@@ -10507,10 +10507,10 @@
         <v>1</v>
       </c>
       <c r="AI16" s="4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AJ16" s="4">
-        <v>8</v>
+        <v>2000</v>
       </c>
       <c r="AK16" s="4" t="b">
         <v>1</v>
@@ -10740,8 +10740,8 @@
       <c r="AC17" s="4">
         <v>-55.707346000000001</v>
       </c>
-      <c r="AD17" s="4" t="b">
-        <v>1</v>
+      <c r="AD17" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE17" s="4" t="s">
         <v>744</v>
@@ -10756,10 +10756,10 @@
         <v>1</v>
       </c>
       <c r="AI17" s="4">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="AJ17" s="4">
-        <v>12</v>
+        <v>2000</v>
       </c>
       <c r="AK17" s="4" t="b">
         <v>1</v>
@@ -10989,8 +10989,8 @@
       <c r="AC18" s="4">
         <v>30.483768999999999</v>
       </c>
-      <c r="AD18" s="4" t="b">
-        <v>1</v>
+      <c r="AD18" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE18" s="4" t="s">
         <v>744</v>
@@ -11005,10 +11005,10 @@
         <v>1</v>
       </c>
       <c r="AI18" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AJ18" s="4">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="AK18" s="4" t="b">
         <v>1</v>
@@ -11238,8 +11238,8 @@
       <c r="AC19" s="4">
         <v>15.735291999999999</v>
       </c>
-      <c r="AD19" s="4" t="b">
-        <v>0</v>
+      <c r="AD19" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE19" s="4" t="s">
         <v>743</v>
@@ -11254,10 +11254,10 @@
         <v>1</v>
       </c>
       <c r="AI19" s="4">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="AJ19" s="4">
-        <v>10</v>
+        <v>2000</v>
       </c>
       <c r="AK19" s="4" t="b">
         <v>1</v>
@@ -11487,8 +11487,8 @@
       <c r="AC20" s="4">
         <v>34.589900999999998</v>
       </c>
-      <c r="AD20" s="4" t="b">
-        <v>1</v>
+      <c r="AD20" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE20" s="4" t="s">
         <v>744</v>
@@ -11503,10 +11503,10 @@
         <v>1</v>
       </c>
       <c r="AI20" s="4">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="AJ20" s="4">
-        <v>7</v>
+        <v>2000</v>
       </c>
       <c r="AK20" s="4" t="b">
         <v>1</v>
@@ -11736,8 +11736,8 @@
       <c r="AC21" s="4">
         <v>-24.680721999999999</v>
       </c>
-      <c r="AD21" s="4" t="b">
-        <v>0</v>
+      <c r="AD21" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE21" s="4" t="s">
         <v>744</v>
@@ -11752,10 +11752,10 @@
         <v>1</v>
       </c>
       <c r="AI21" s="4">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="AJ21" s="4">
-        <v>2</v>
+        <v>2000</v>
       </c>
       <c r="AK21" s="4" t="b">
         <v>1</v>
@@ -11985,8 +11985,8 @@
       <c r="AC22" s="4">
         <v>-82.543801999999999</v>
       </c>
-      <c r="AD22" s="4" t="b">
-        <v>1</v>
+      <c r="AD22" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE22" s="4" t="s">
         <v>743</v>
@@ -12001,10 +12001,10 @@
         <v>1</v>
       </c>
       <c r="AI22" s="4">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AJ22" s="4">
-        <v>5</v>
+        <v>2000</v>
       </c>
       <c r="AK22" s="4" t="b">
         <v>1</v>
@@ -12234,8 +12234,8 @@
       <c r="AC23" s="4">
         <v>-87.080423999999994</v>
       </c>
-      <c r="AD23" s="4" t="b">
-        <v>0</v>
+      <c r="AD23" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE23" s="4" t="s">
         <v>743</v>
@@ -12250,10 +12250,10 @@
         <v>1</v>
       </c>
       <c r="AI23" s="4">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="AJ23" s="4">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="AK23" s="4" t="b">
         <v>1</v>
@@ -12483,8 +12483,8 @@
       <c r="AC24" s="4">
         <v>7.4440400000000002</v>
       </c>
-      <c r="AD24" s="4" t="b">
-        <v>0</v>
+      <c r="AD24" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE24" s="4" t="s">
         <v>743</v>
@@ -12499,10 +12499,10 @@
         <v>1</v>
       </c>
       <c r="AI24" s="4">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AJ24" s="4">
-        <v>12</v>
+        <v>2000</v>
       </c>
       <c r="AK24" s="4" t="b">
         <v>1</v>
@@ -12732,8 +12732,8 @@
       <c r="AC25" s="4">
         <v>-79.738702000000004</v>
       </c>
-      <c r="AD25" s="4" t="b">
-        <v>1</v>
+      <c r="AD25" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE25" s="4" t="s">
         <v>743</v>
@@ -12748,10 +12748,10 @@
         <v>1</v>
       </c>
       <c r="AI25" s="4">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="AJ25" s="4">
-        <v>6</v>
+        <v>2000</v>
       </c>
       <c r="AK25" s="4" t="b">
         <v>1</v>
@@ -12981,8 +12981,8 @@
       <c r="AC26" s="4">
         <v>-12.369664</v>
       </c>
-      <c r="AD26" s="4" t="b">
-        <v>1</v>
+      <c r="AD26" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE26" s="4" t="s">
         <v>743</v>
@@ -12997,10 +12997,10 @@
         <v>1</v>
       </c>
       <c r="AI26" s="4">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="AJ26" s="4">
-        <v>4</v>
+        <v>2000</v>
       </c>
       <c r="AK26" s="4" t="b">
         <v>1</v>
@@ -13230,8 +13230,8 @@
       <c r="AC27" s="4">
         <v>20.572801999999999</v>
       </c>
-      <c r="AD27" s="4" t="b">
-        <v>1</v>
+      <c r="AD27" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE27" s="4" t="s">
         <v>743</v>
@@ -13246,10 +13246,10 @@
         <v>1</v>
       </c>
       <c r="AI27" s="4">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="AJ27" s="4">
-        <v>6</v>
+        <v>2000</v>
       </c>
       <c r="AK27" s="4" t="b">
         <v>1</v>
@@ -13479,8 +13479,8 @@
       <c r="AC28" s="4">
         <v>-85.982280000000003</v>
       </c>
-      <c r="AD28" s="4" t="b">
-        <v>0</v>
+      <c r="AD28" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE28" s="4" t="s">
         <v>743</v>
@@ -13495,10 +13495,10 @@
         <v>1</v>
       </c>
       <c r="AI28" s="4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AJ28" s="4">
-        <v>2</v>
+        <v>2000</v>
       </c>
       <c r="AK28" s="4" t="b">
         <v>1</v>
@@ -13728,8 +13728,8 @@
       <c r="AC29" s="4">
         <v>56.726424999999999</v>
       </c>
-      <c r="AD29" s="4" t="b">
-        <v>0</v>
+      <c r="AD29" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE29" s="4" t="s">
         <v>744</v>
@@ -13744,10 +13744,10 @@
         <v>1</v>
       </c>
       <c r="AI29" s="4">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="AJ29" s="4">
-        <v>6</v>
+        <v>2000</v>
       </c>
       <c r="AK29" s="4" t="b">
         <v>1</v>
@@ -13977,8 +13977,8 @@
       <c r="AC30" s="4">
         <v>-88.760797999999994</v>
       </c>
-      <c r="AD30" s="4" t="b">
-        <v>1</v>
+      <c r="AD30" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE30" s="4" t="s">
         <v>743</v>
@@ -13993,10 +13993,10 @@
         <v>1</v>
       </c>
       <c r="AI30" s="4">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AJ30" s="4">
-        <v>2</v>
+        <v>2000</v>
       </c>
       <c r="AK30" s="4" t="b">
         <v>1</v>
@@ -14226,8 +14226,8 @@
       <c r="AC31" s="4">
         <v>22.479443</v>
       </c>
-      <c r="AD31" s="4" t="b">
-        <v>1</v>
+      <c r="AD31" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE31" s="4" t="s">
         <v>744</v>
@@ -14242,10 +14242,10 @@
         <v>1</v>
       </c>
       <c r="AI31" s="4">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="AJ31" s="4">
-        <v>5</v>
+        <v>2000</v>
       </c>
       <c r="AK31" s="4" t="b">
         <v>1</v>
@@ -14475,8 +14475,8 @@
       <c r="AC32" s="4">
         <v>-51.119917999999998</v>
       </c>
-      <c r="AD32" s="4" t="b">
-        <v>0</v>
+      <c r="AD32" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE32" s="4" t="s">
         <v>744</v>
@@ -14491,10 +14491,10 @@
         <v>1</v>
       </c>
       <c r="AI32" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AJ32" s="4">
-        <v>12</v>
+        <v>2000</v>
       </c>
       <c r="AK32" s="4" t="b">
         <v>1</v>
@@ -14722,8 +14722,8 @@
       <c r="AC33" s="4">
         <v>15.550630999999999</v>
       </c>
-      <c r="AD33" s="4" t="b">
-        <v>1</v>
+      <c r="AD33" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE33" s="4" t="s">
         <v>743</v>
@@ -14738,10 +14738,10 @@
         <v>1</v>
       </c>
       <c r="AI33" s="4">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="AJ33" s="4">
-        <v>11</v>
+        <v>2000</v>
       </c>
       <c r="AK33" s="4" t="b">
         <v>1</v>
@@ -14969,8 +14969,8 @@
       <c r="AC34" s="4">
         <v>-20.801469999999998</v>
       </c>
-      <c r="AD34" s="4" t="b">
-        <v>1</v>
+      <c r="AD34" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE34" s="4" t="s">
         <v>743</v>
@@ -14985,10 +14985,10 @@
         <v>1</v>
       </c>
       <c r="AI34" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AJ34" s="4">
-        <v>8</v>
+        <v>2000</v>
       </c>
       <c r="AK34" s="4" t="b">
         <v>1</v>
@@ -15216,8 +15216,8 @@
       <c r="AC35" s="4">
         <v>-50.650393000000001</v>
       </c>
-      <c r="AD35" s="4" t="b">
-        <v>1</v>
+      <c r="AD35" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE35" s="4" t="s">
         <v>744</v>
@@ -15232,10 +15232,10 @@
         <v>1</v>
       </c>
       <c r="AI35" s="4">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="AJ35" s="4">
-        <v>10</v>
+        <v>2000</v>
       </c>
       <c r="AK35" s="4" t="b">
         <v>1</v>
@@ -15463,8 +15463,8 @@
       <c r="AC36" s="4">
         <v>-12.745844</v>
       </c>
-      <c r="AD36" s="4" t="b">
-        <v>1</v>
+      <c r="AD36" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE36" s="4" t="s">
         <v>744</v>
@@ -15479,10 +15479,10 @@
         <v>1</v>
       </c>
       <c r="AI36" s="4">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="AJ36" s="4">
-        <v>5</v>
+        <v>2000</v>
       </c>
       <c r="AK36" s="4" t="b">
         <v>1</v>
@@ -15710,8 +15710,8 @@
       <c r="AC37" s="4">
         <v>86.357771</v>
       </c>
-      <c r="AD37" s="4" t="b">
-        <v>1</v>
+      <c r="AD37" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE37" s="4" t="s">
         <v>744</v>
@@ -15726,10 +15726,10 @@
         <v>1</v>
       </c>
       <c r="AI37" s="4">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="AJ37" s="4">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="AK37" s="4" t="b">
         <v>1</v>
@@ -15957,8 +15957,8 @@
       <c r="AC38" s="4">
         <v>-53.419744000000001</v>
       </c>
-      <c r="AD38" s="4" t="b">
-        <v>1</v>
+      <c r="AD38" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE38" s="4" t="s">
         <v>743</v>
@@ -15973,10 +15973,10 @@
         <v>1</v>
       </c>
       <c r="AI38" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AJ38" s="4">
-        <v>2</v>
+        <v>2000</v>
       </c>
       <c r="AK38" s="4" t="b">
         <v>1</v>
@@ -16204,8 +16204,8 @@
       <c r="AC39" s="4">
         <v>39.026747</v>
       </c>
-      <c r="AD39" s="4" t="b">
-        <v>1</v>
+      <c r="AD39" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE39" s="4" t="s">
         <v>744</v>
@@ -16220,10 +16220,10 @@
         <v>1</v>
       </c>
       <c r="AI39" s="4">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="AJ39" s="4">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="AK39" s="4" t="b">
         <v>1</v>
@@ -16451,8 +16451,8 @@
       <c r="AC40" s="4">
         <v>-42.983173999999998</v>
       </c>
-      <c r="AD40" s="4" t="b">
-        <v>1</v>
+      <c r="AD40" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE40" s="4" t="s">
         <v>743</v>
@@ -16467,10 +16467,10 @@
         <v>1</v>
       </c>
       <c r="AI40" s="4">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="AJ40" s="4">
-        <v>8</v>
+        <v>2000</v>
       </c>
       <c r="AK40" s="4" t="b">
         <v>1</v>
@@ -16698,8 +16698,8 @@
       <c r="AC41" s="4">
         <v>5.3500759999999996</v>
       </c>
-      <c r="AD41" s="4" t="b">
-        <v>0</v>
+      <c r="AD41" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE41" s="4" t="s">
         <v>744</v>
@@ -16714,10 +16714,10 @@
         <v>1</v>
       </c>
       <c r="AI41" s="4">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="AJ41" s="4">
-        <v>8</v>
+        <v>2000</v>
       </c>
       <c r="AK41" s="4" t="b">
         <v>1</v>
@@ -16945,8 +16945,8 @@
       <c r="AC42" s="4">
         <v>77.702226999999993</v>
       </c>
-      <c r="AD42" s="4" t="b">
-        <v>0</v>
+      <c r="AD42" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE42" s="4" t="s">
         <v>744</v>
@@ -16961,10 +16961,10 @@
         <v>1</v>
       </c>
       <c r="AI42" s="4">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="AJ42" s="4">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="AK42" s="4" t="b">
         <v>1</v>
@@ -17192,8 +17192,8 @@
       <c r="AC43" s="4">
         <v>40.733637000000002</v>
       </c>
-      <c r="AD43" s="4" t="b">
-        <v>0</v>
+      <c r="AD43" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE43" s="4" t="s">
         <v>744</v>
@@ -17208,10 +17208,10 @@
         <v>1</v>
       </c>
       <c r="AI43" s="4">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="AJ43" s="4">
-        <v>8</v>
+        <v>2000</v>
       </c>
       <c r="AK43" s="4" t="b">
         <v>1</v>
@@ -17439,8 +17439,8 @@
       <c r="AC44" s="4">
         <v>-85.102323999999996</v>
       </c>
-      <c r="AD44" s="4" t="b">
-        <v>0</v>
+      <c r="AD44" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE44" s="4" t="s">
         <v>743</v>
@@ -17455,10 +17455,10 @@
         <v>1</v>
       </c>
       <c r="AI44" s="4">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="AJ44" s="4">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="AK44" s="4" t="b">
         <v>1</v>
@@ -17686,8 +17686,8 @@
       <c r="AC45" s="4">
         <v>73.506962999999999</v>
       </c>
-      <c r="AD45" s="4" t="b">
-        <v>1</v>
+      <c r="AD45" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE45" s="4" t="s">
         <v>744</v>
@@ -17702,10 +17702,10 @@
         <v>1</v>
       </c>
       <c r="AI45" s="4">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="AJ45" s="4">
-        <v>12</v>
+        <v>2000</v>
       </c>
       <c r="AK45" s="4" t="b">
         <v>1</v>
@@ -17933,8 +17933,8 @@
       <c r="AC46" s="4">
         <v>42.401240999999999</v>
       </c>
-      <c r="AD46" s="4" t="b">
-        <v>0</v>
+      <c r="AD46" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE46" s="4" t="s">
         <v>744</v>
@@ -17949,10 +17949,10 @@
         <v>1</v>
       </c>
       <c r="AI46" s="4">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="AJ46" s="4">
-        <v>8</v>
+        <v>2000</v>
       </c>
       <c r="AK46" s="4" t="b">
         <v>1</v>
@@ -18180,8 +18180,8 @@
       <c r="AC47" s="4">
         <v>-23.544350999999999</v>
       </c>
-      <c r="AD47" s="4" t="b">
-        <v>1</v>
+      <c r="AD47" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE47" s="4" t="s">
         <v>743</v>
@@ -18199,7 +18199,7 @@
         <v>1</v>
       </c>
       <c r="AJ47" s="4">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="AK47" s="4" t="b">
         <v>1</v>
@@ -18427,8 +18427,8 @@
       <c r="AC48" s="4">
         <v>-22.835816000000001</v>
       </c>
-      <c r="AD48" s="4" t="b">
-        <v>1</v>
+      <c r="AD48" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE48" s="4" t="s">
         <v>743</v>
@@ -18443,10 +18443,10 @@
         <v>1</v>
       </c>
       <c r="AI48" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AJ48" s="4">
-        <v>2</v>
+        <v>2000</v>
       </c>
       <c r="AK48" s="4" t="b">
         <v>1</v>
@@ -18674,8 +18674,8 @@
       <c r="AC49" s="4">
         <v>-42.658614</v>
       </c>
-      <c r="AD49" s="4" t="b">
-        <v>0</v>
+      <c r="AD49" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE49" s="4" t="s">
         <v>743</v>
@@ -18690,10 +18690,10 @@
         <v>1</v>
       </c>
       <c r="AI49" s="4">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="AJ49" s="4">
-        <v>7</v>
+        <v>2000</v>
       </c>
       <c r="AK49" s="4" t="b">
         <v>1</v>
@@ -18921,8 +18921,8 @@
       <c r="AC50" s="4">
         <v>-19.407806999999998</v>
       </c>
-      <c r="AD50" s="4" t="b">
-        <v>1</v>
+      <c r="AD50" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE50" s="4" t="s">
         <v>743</v>
@@ -18937,10 +18937,10 @@
         <v>1</v>
       </c>
       <c r="AI50" s="4">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="AJ50" s="4">
-        <v>9</v>
+        <v>2000</v>
       </c>
       <c r="AK50" s="4" t="b">
         <v>1</v>
@@ -19168,8 +19168,8 @@
       <c r="AC51" s="4">
         <v>9.3679240000000004</v>
       </c>
-      <c r="AD51" s="4" t="b">
-        <v>1</v>
+      <c r="AD51" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE51" s="4" t="s">
         <v>743</v>
@@ -19184,10 +19184,10 @@
         <v>1</v>
       </c>
       <c r="AI51" s="4">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="AJ51" s="4">
-        <v>9</v>
+        <v>2000</v>
       </c>
       <c r="AK51" s="4" t="b">
         <v>1</v>
@@ -19415,8 +19415,8 @@
       <c r="AC52" s="4">
         <v>41.783698000000001</v>
       </c>
-      <c r="AD52" s="4" t="b">
-        <v>0</v>
+      <c r="AD52" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE52" s="4" t="s">
         <v>744</v>
@@ -19431,10 +19431,10 @@
         <v>1</v>
       </c>
       <c r="AI52" s="4">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AJ52" s="4">
-        <v>8</v>
+        <v>2000</v>
       </c>
       <c r="AK52" s="4" t="b">
         <v>1</v>
@@ -19662,8 +19662,8 @@
       <c r="AC53" s="4">
         <v>-42.128430999999999</v>
       </c>
-      <c r="AD53" s="4" t="b">
-        <v>1</v>
+      <c r="AD53" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE53" s="4" t="s">
         <v>744</v>
@@ -19678,10 +19678,10 @@
         <v>1</v>
       </c>
       <c r="AI53" s="4">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AJ53" s="4">
-        <v>6</v>
+        <v>2000</v>
       </c>
       <c r="AK53" s="4" t="b">
         <v>1</v>
@@ -19909,8 +19909,8 @@
       <c r="AC54" s="4">
         <v>-9.9101060000000007</v>
       </c>
-      <c r="AD54" s="4" t="b">
-        <v>0</v>
+      <c r="AD54" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE54" s="4" t="s">
         <v>744</v>
@@ -19925,10 +19925,10 @@
         <v>1</v>
       </c>
       <c r="AI54" s="4">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="AJ54" s="4">
-        <v>12</v>
+        <v>2000</v>
       </c>
       <c r="AK54" s="4" t="b">
         <v>1</v>
@@ -20156,8 +20156,8 @@
       <c r="AC55" s="4">
         <v>6.0062879999999996</v>
       </c>
-      <c r="AD55" s="4" t="b">
-        <v>0</v>
+      <c r="AD55" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE55" s="4" t="s">
         <v>744</v>
@@ -20172,10 +20172,10 @@
         <v>1</v>
       </c>
       <c r="AI55" s="4">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="AJ55" s="4">
-        <v>8</v>
+        <v>2000</v>
       </c>
       <c r="AK55" s="4" t="b">
         <v>1</v>
@@ -20403,8 +20403,8 @@
       <c r="AC56" s="4">
         <v>34.276311</v>
       </c>
-      <c r="AD56" s="4" t="b">
-        <v>1</v>
+      <c r="AD56" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE56" s="4" t="s">
         <v>744</v>
@@ -20419,10 +20419,10 @@
         <v>1</v>
       </c>
       <c r="AI56" s="4">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="AJ56" s="4">
-        <v>12</v>
+        <v>2000</v>
       </c>
       <c r="AK56" s="4" t="b">
         <v>1</v>
@@ -20650,8 +20650,8 @@
       <c r="AC57" s="4">
         <v>-72.209366000000003</v>
       </c>
-      <c r="AD57" s="4" t="b">
-        <v>1</v>
+      <c r="AD57" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE57" s="4" t="s">
         <v>744</v>
@@ -20666,10 +20666,10 @@
         <v>1</v>
       </c>
       <c r="AI57" s="4">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AJ57" s="4">
-        <v>5</v>
+        <v>2000</v>
       </c>
       <c r="AK57" s="4" t="b">
         <v>1</v>
@@ -20897,8 +20897,8 @@
       <c r="AC58" s="4">
         <v>5.8631380000000002</v>
       </c>
-      <c r="AD58" s="4" t="b">
-        <v>1</v>
+      <c r="AD58" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE58" s="4" t="s">
         <v>744</v>
@@ -20913,10 +20913,10 @@
         <v>1</v>
       </c>
       <c r="AI58" s="4">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="AJ58" s="4">
-        <v>4</v>
+        <v>2000</v>
       </c>
       <c r="AK58" s="4" t="b">
         <v>1</v>
@@ -21144,8 +21144,8 @@
       <c r="AC59" s="4">
         <v>-83.546226000000004</v>
       </c>
-      <c r="AD59" s="4" t="b">
-        <v>0</v>
+      <c r="AD59" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE59" s="4" t="s">
         <v>744</v>
@@ -21160,10 +21160,10 @@
         <v>1</v>
       </c>
       <c r="AI59" s="4">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="AJ59" s="4">
-        <v>8</v>
+        <v>2000</v>
       </c>
       <c r="AK59" s="4" t="b">
         <v>1</v>
@@ -21391,8 +21391,8 @@
       <c r="AC60" s="4">
         <v>35.938450000000003</v>
       </c>
-      <c r="AD60" s="4" t="b">
-        <v>1</v>
+      <c r="AD60" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE60" s="4" t="s">
         <v>744</v>
@@ -21410,7 +21410,7 @@
         <v>1</v>
       </c>
       <c r="AJ60" s="4">
-        <v>7</v>
+        <v>2000</v>
       </c>
       <c r="AK60" s="4" t="b">
         <v>1</v>
@@ -21638,8 +21638,8 @@
       <c r="AC61" s="4">
         <v>14.463884</v>
       </c>
-      <c r="AD61" s="4" t="b">
-        <v>1</v>
+      <c r="AD61" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE61" s="4" t="s">
         <v>743</v>
@@ -21654,10 +21654,10 @@
         <v>1</v>
       </c>
       <c r="AI61" s="4">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="AJ61" s="4">
-        <v>8</v>
+        <v>2000</v>
       </c>
       <c r="AK61" s="4" t="b">
         <v>1</v>
@@ -21885,8 +21885,8 @@
       <c r="AC62" s="4">
         <v>-86.819407999999996</v>
       </c>
-      <c r="AD62" s="4" t="b">
-        <v>0</v>
+      <c r="AD62" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE62" s="4" t="s">
         <v>743</v>
@@ -21901,10 +21901,10 @@
         <v>1</v>
       </c>
       <c r="AI62" s="4">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="AJ62" s="4">
-        <v>8</v>
+        <v>2000</v>
       </c>
       <c r="AK62" s="4" t="b">
         <v>1</v>
@@ -22132,8 +22132,8 @@
       <c r="AC63" s="4">
         <v>77.658058999999994</v>
       </c>
-      <c r="AD63" s="4" t="b">
-        <v>1</v>
+      <c r="AD63" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE63" s="4" t="s">
         <v>743</v>
@@ -22148,10 +22148,10 @@
         <v>1</v>
       </c>
       <c r="AI63" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AJ63" s="4">
-        <v>12</v>
+        <v>2000</v>
       </c>
       <c r="AK63" s="4" t="b">
         <v>1</v>
@@ -22379,8 +22379,8 @@
       <c r="AC64" s="4">
         <v>31.803820999999999</v>
       </c>
-      <c r="AD64" s="4" t="b">
-        <v>0</v>
+      <c r="AD64" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE64" s="4" t="s">
         <v>743</v>
@@ -22395,10 +22395,10 @@
         <v>1</v>
       </c>
       <c r="AI64" s="4">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AJ64" s="4">
-        <v>12</v>
+        <v>2000</v>
       </c>
       <c r="AK64" s="4" t="b">
         <v>1</v>
@@ -22626,8 +22626,8 @@
       <c r="AC65" s="4">
         <v>32.120038000000001</v>
       </c>
-      <c r="AD65" s="4" t="b">
-        <v>0</v>
+      <c r="AD65" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE65" s="4" t="s">
         <v>743</v>
@@ -22642,10 +22642,10 @@
         <v>1</v>
       </c>
       <c r="AI65" s="4">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AJ65" s="4">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="AK65" s="4" t="b">
         <v>1</v>
@@ -22873,8 +22873,8 @@
       <c r="AC66" s="4">
         <v>84.164443000000006</v>
       </c>
-      <c r="AD66" s="4" t="b">
-        <v>1</v>
+      <c r="AD66" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE66" s="4" t="s">
         <v>744</v>
@@ -22889,10 +22889,10 @@
         <v>1</v>
       </c>
       <c r="AI66" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AJ66" s="4">
-        <v>12</v>
+        <v>2000</v>
       </c>
       <c r="AK66" s="4" t="b">
         <v>1</v>
@@ -23120,8 +23120,8 @@
       <c r="AC67" s="4">
         <v>48.472589999999997</v>
       </c>
-      <c r="AD67" s="4" t="b">
-        <v>1</v>
+      <c r="AD67" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE67" s="4" t="s">
         <v>744</v>
@@ -23136,10 +23136,10 @@
         <v>1</v>
       </c>
       <c r="AI67" s="4">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AJ67" s="4">
-        <v>12</v>
+        <v>2000</v>
       </c>
       <c r="AK67" s="4" t="b">
         <v>1</v>
@@ -23367,8 +23367,8 @@
       <c r="AC68" s="4">
         <v>-39.848564000000003</v>
       </c>
-      <c r="AD68" s="4" t="b">
-        <v>1</v>
+      <c r="AD68" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE68" s="4" t="s">
         <v>743</v>
@@ -23383,10 +23383,10 @@
         <v>1</v>
       </c>
       <c r="AI68" s="4">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="AJ68" s="4">
-        <v>6</v>
+        <v>2000</v>
       </c>
       <c r="AK68" s="4" t="b">
         <v>1</v>
@@ -23614,8 +23614,8 @@
       <c r="AC69" s="4">
         <v>83.801181</v>
       </c>
-      <c r="AD69" s="4" t="b">
-        <v>1</v>
+      <c r="AD69" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE69" s="4" t="s">
         <v>744</v>
@@ -23630,10 +23630,10 @@
         <v>1</v>
       </c>
       <c r="AI69" s="4">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AJ69" s="4">
-        <v>9</v>
+        <v>2000</v>
       </c>
       <c r="AK69" s="4" t="b">
         <v>1</v>
@@ -23861,8 +23861,8 @@
       <c r="AC70" s="4">
         <v>60.450898000000002</v>
       </c>
-      <c r="AD70" s="4" t="b">
-        <v>0</v>
+      <c r="AD70" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE70" s="4" t="s">
         <v>743</v>
@@ -23877,10 +23877,10 @@
         <v>1</v>
       </c>
       <c r="AI70" s="4">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="AJ70" s="4">
-        <v>2</v>
+        <v>2000</v>
       </c>
       <c r="AK70" s="4" t="b">
         <v>1</v>
@@ -24108,8 +24108,8 @@
       <c r="AC71" s="4">
         <v>-1.6736610000000001</v>
       </c>
-      <c r="AD71" s="4" t="b">
-        <v>1</v>
+      <c r="AD71" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE71" s="4" t="s">
         <v>743</v>
@@ -24124,10 +24124,10 @@
         <v>1</v>
       </c>
       <c r="AI71" s="4">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="AJ71" s="4">
-        <v>2</v>
+        <v>2000</v>
       </c>
       <c r="AK71" s="4" t="b">
         <v>1</v>
@@ -24355,8 +24355,8 @@
       <c r="AC72" s="4">
         <v>-49.898896999999998</v>
       </c>
-      <c r="AD72" s="4" t="b">
-        <v>0</v>
+      <c r="AD72" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE72" s="4" t="s">
         <v>744</v>
@@ -24371,10 +24371,10 @@
         <v>1</v>
       </c>
       <c r="AI72" s="4">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="AJ72" s="4">
-        <v>9</v>
+        <v>2000</v>
       </c>
       <c r="AK72" s="4" t="b">
         <v>1</v>
@@ -24602,8 +24602,8 @@
       <c r="AC73" s="4">
         <v>-88.252052000000006</v>
       </c>
-      <c r="AD73" s="4" t="b">
-        <v>1</v>
+      <c r="AD73" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE73" s="4" t="s">
         <v>743</v>
@@ -24618,10 +24618,10 @@
         <v>1</v>
       </c>
       <c r="AI73" s="4">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="AJ73" s="4">
-        <v>8</v>
+        <v>2000</v>
       </c>
       <c r="AK73" s="4" t="b">
         <v>1</v>
@@ -24849,8 +24849,8 @@
       <c r="AC74" s="4">
         <v>-80.698436999999998</v>
       </c>
-      <c r="AD74" s="4" t="b">
-        <v>0</v>
+      <c r="AD74" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE74" s="4" t="s">
         <v>744</v>
@@ -24865,10 +24865,10 @@
         <v>1</v>
       </c>
       <c r="AI74" s="4">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="AJ74" s="4">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="AK74" s="4" t="b">
         <v>1</v>
@@ -25096,8 +25096,8 @@
       <c r="AC75" s="4">
         <v>76.463364999999996</v>
       </c>
-      <c r="AD75" s="4" t="b">
-        <v>0</v>
+      <c r="AD75" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE75" s="4" t="s">
         <v>743</v>
@@ -25112,10 +25112,10 @@
         <v>1</v>
       </c>
       <c r="AI75" s="4">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="AJ75" s="4">
-        <v>7</v>
+        <v>2000</v>
       </c>
       <c r="AK75" s="4" t="b">
         <v>1</v>
@@ -25343,8 +25343,8 @@
       <c r="AC76" s="4">
         <v>-87.346996000000004</v>
       </c>
-      <c r="AD76" s="4" t="b">
-        <v>0</v>
+      <c r="AD76" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE76" s="4" t="s">
         <v>743</v>
@@ -25359,10 +25359,10 @@
         <v>1</v>
       </c>
       <c r="AI76" s="4">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="AJ76" s="4">
-        <v>11</v>
+        <v>2000</v>
       </c>
       <c r="AK76" s="4" t="b">
         <v>1</v>
@@ -25590,8 +25590,8 @@
       <c r="AC77" s="4">
         <v>-22.680685</v>
       </c>
-      <c r="AD77" s="4" t="b">
-        <v>1</v>
+      <c r="AD77" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE77" s="4" t="s">
         <v>744</v>
@@ -25606,10 +25606,10 @@
         <v>1</v>
       </c>
       <c r="AI77" s="4">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AJ77" s="4">
-        <v>4</v>
+        <v>2000</v>
       </c>
       <c r="AK77" s="4" t="b">
         <v>1</v>
@@ -25837,8 +25837,8 @@
       <c r="AC78" s="4">
         <v>-81.095416</v>
       </c>
-      <c r="AD78" s="4" t="b">
-        <v>0</v>
+      <c r="AD78" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE78" s="4" t="s">
         <v>743</v>
@@ -25853,10 +25853,10 @@
         <v>1</v>
       </c>
       <c r="AI78" s="4">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="AJ78" s="4">
-        <v>6</v>
+        <v>2000</v>
       </c>
       <c r="AK78" s="4" t="b">
         <v>1</v>
@@ -26084,8 +26084,8 @@
       <c r="AC79" s="4">
         <v>-19.985899</v>
       </c>
-      <c r="AD79" s="4" t="b">
-        <v>0</v>
+      <c r="AD79" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE79" s="4" t="s">
         <v>743</v>
@@ -26100,10 +26100,10 @@
         <v>1</v>
       </c>
       <c r="AI79" s="4">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="AJ79" s="4">
-        <v>10</v>
+        <v>2000</v>
       </c>
       <c r="AK79" s="4" t="b">
         <v>1</v>
@@ -26331,8 +26331,8 @@
       <c r="AC80" s="4">
         <v>56.470187000000003</v>
       </c>
-      <c r="AD80" s="4" t="b">
-        <v>0</v>
+      <c r="AD80" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE80" s="4" t="s">
         <v>743</v>
@@ -26347,10 +26347,10 @@
         <v>1</v>
       </c>
       <c r="AI80" s="4">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="AJ80" s="4">
-        <v>2</v>
+        <v>2000</v>
       </c>
       <c r="AK80" s="4" t="b">
         <v>1</v>
@@ -26578,8 +26578,8 @@
       <c r="AC81" s="4">
         <v>-12.410323999999999</v>
       </c>
-      <c r="AD81" s="4" t="b">
-        <v>0</v>
+      <c r="AD81" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE81" s="4" t="s">
         <v>743</v>
@@ -26594,10 +26594,10 @@
         <v>1</v>
       </c>
       <c r="AI81" s="4">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="AJ81" s="4">
-        <v>3</v>
+        <v>2000</v>
       </c>
       <c r="AK81" s="4" t="b">
         <v>1</v>
@@ -26825,8 +26825,8 @@
       <c r="AC82" s="4">
         <v>19.058785</v>
       </c>
-      <c r="AD82" s="4" t="b">
-        <v>0</v>
+      <c r="AD82" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE82" s="4" t="s">
         <v>743</v>
@@ -26841,10 +26841,10 @@
         <v>1</v>
       </c>
       <c r="AI82" s="4">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="AJ82" s="4">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="AK82" s="4" t="b">
         <v>1</v>
@@ -27072,8 +27072,8 @@
       <c r="AC83" s="4">
         <v>66.777368999999993</v>
       </c>
-      <c r="AD83" s="4" t="b">
-        <v>1</v>
+      <c r="AD83" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE83" s="4" t="s">
         <v>743</v>
@@ -27088,10 +27088,10 @@
         <v>1</v>
       </c>
       <c r="AI83" s="4">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="AJ83" s="4">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="AK83" s="4" t="b">
         <v>1</v>
@@ -27319,8 +27319,8 @@
       <c r="AC84" s="4">
         <v>71.080763000000005</v>
       </c>
-      <c r="AD84" s="4" t="b">
-        <v>1</v>
+      <c r="AD84" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE84" s="4" t="s">
         <v>743</v>
@@ -27335,10 +27335,10 @@
         <v>1</v>
       </c>
       <c r="AI84" s="4">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="AJ84" s="4">
-        <v>7</v>
+        <v>2000</v>
       </c>
       <c r="AK84" s="4" t="b">
         <v>1</v>
@@ -27566,8 +27566,8 @@
       <c r="AC85" s="4">
         <v>14.137574000000001</v>
       </c>
-      <c r="AD85" s="4" t="b">
-        <v>0</v>
+      <c r="AD85" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE85" s="4" t="s">
         <v>744</v>
@@ -27582,10 +27582,10 @@
         <v>1</v>
       </c>
       <c r="AI85" s="4">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="AJ85" s="4">
-        <v>2</v>
+        <v>2000</v>
       </c>
       <c r="AK85" s="4" t="b">
         <v>1</v>
@@ -27813,8 +27813,8 @@
       <c r="AC86" s="4">
         <v>51.336674000000002</v>
       </c>
-      <c r="AD86" s="4" t="b">
-        <v>1</v>
+      <c r="AD86" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE86" s="4" t="s">
         <v>743</v>
@@ -27829,10 +27829,10 @@
         <v>1</v>
       </c>
       <c r="AI86" s="4">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="AJ86" s="4">
-        <v>5</v>
+        <v>2000</v>
       </c>
       <c r="AK86" s="4" t="b">
         <v>1</v>
@@ -28060,8 +28060,8 @@
       <c r="AC87" s="4">
         <v>-56.184035999999999</v>
       </c>
-      <c r="AD87" s="4" t="b">
-        <v>0</v>
+      <c r="AD87" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE87" s="4" t="s">
         <v>744</v>
@@ -28076,10 +28076,10 @@
         <v>1</v>
       </c>
       <c r="AI87" s="4">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AJ87" s="4">
-        <v>3</v>
+        <v>2000</v>
       </c>
       <c r="AK87" s="4" t="b">
         <v>1</v>
@@ -28307,8 +28307,8 @@
       <c r="AC88" s="4">
         <v>28.223075999999999</v>
       </c>
-      <c r="AD88" s="4" t="b">
-        <v>1</v>
+      <c r="AD88" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE88" s="4" t="s">
         <v>744</v>
@@ -28323,10 +28323,10 @@
         <v>1</v>
       </c>
       <c r="AI88" s="4">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="AJ88" s="4">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="AK88" s="4" t="b">
         <v>1</v>
@@ -28554,8 +28554,8 @@
       <c r="AC89" s="4">
         <v>-11.822024000000001</v>
       </c>
-      <c r="AD89" s="4" t="b">
-        <v>1</v>
+      <c r="AD89" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE89" s="4" t="s">
         <v>743</v>
@@ -28570,10 +28570,10 @@
         <v>1</v>
       </c>
       <c r="AI89" s="4">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="AJ89" s="4">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="AK89" s="4" t="b">
         <v>1</v>
@@ -28801,8 +28801,8 @@
       <c r="AC90" s="4">
         <v>-36.676758</v>
       </c>
-      <c r="AD90" s="4" t="b">
-        <v>1</v>
+      <c r="AD90" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE90" s="4" t="s">
         <v>744</v>
@@ -28817,10 +28817,10 @@
         <v>1</v>
       </c>
       <c r="AI90" s="4">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="AJ90" s="4">
-        <v>12</v>
+        <v>2000</v>
       </c>
       <c r="AK90" s="4" t="b">
         <v>1</v>
@@ -29048,8 +29048,8 @@
       <c r="AC91" s="4">
         <v>-80.129637000000002</v>
       </c>
-      <c r="AD91" s="4" t="b">
-        <v>1</v>
+      <c r="AD91" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE91" s="4" t="s">
         <v>743</v>
@@ -29064,10 +29064,10 @@
         <v>1</v>
       </c>
       <c r="AI91" s="4">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="AJ91" s="4">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="AK91" s="4" t="b">
         <v>1</v>
@@ -29295,8 +29295,8 @@
       <c r="AC92" s="4">
         <v>-89.385095000000007</v>
       </c>
-      <c r="AD92" s="4" t="b">
-        <v>0</v>
+      <c r="AD92" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE92" s="4" t="s">
         <v>743</v>
@@ -29311,10 +29311,10 @@
         <v>1</v>
       </c>
       <c r="AI92" s="4">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="AJ92" s="4">
-        <v>10</v>
+        <v>2000</v>
       </c>
       <c r="AK92" s="4" t="b">
         <v>1</v>
@@ -29542,8 +29542,8 @@
       <c r="AC93" s="4">
         <v>25.803301999999999</v>
       </c>
-      <c r="AD93" s="4" t="b">
-        <v>1</v>
+      <c r="AD93" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE93" s="4" t="s">
         <v>744</v>
@@ -29558,10 +29558,10 @@
         <v>1</v>
       </c>
       <c r="AI93" s="4">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="AJ93" s="4">
-        <v>9</v>
+        <v>2000</v>
       </c>
       <c r="AK93" s="4" t="b">
         <v>1</v>
@@ -29789,8 +29789,8 @@
       <c r="AC94" s="4">
         <v>-5.51546</v>
       </c>
-      <c r="AD94" s="4" t="b">
-        <v>1</v>
+      <c r="AD94" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE94" s="4" t="s">
         <v>743</v>
@@ -29805,10 +29805,10 @@
         <v>1</v>
       </c>
       <c r="AI94" s="4">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="AJ94" s="4">
-        <v>12</v>
+        <v>2000</v>
       </c>
       <c r="AK94" s="4" t="b">
         <v>1</v>
@@ -30036,8 +30036,8 @@
       <c r="AC95" s="4">
         <v>-47.299477000000003</v>
       </c>
-      <c r="AD95" s="4" t="b">
-        <v>0</v>
+      <c r="AD95" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE95" s="4" t="s">
         <v>743</v>
@@ -30052,10 +30052,10 @@
         <v>1</v>
       </c>
       <c r="AI95" s="4">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="AJ95" s="4">
-        <v>7</v>
+        <v>2000</v>
       </c>
       <c r="AK95" s="4" t="b">
         <v>1</v>
@@ -30283,8 +30283,8 @@
       <c r="AC96" s="4">
         <v>11.267817000000001</v>
       </c>
-      <c r="AD96" s="4" t="b">
-        <v>1</v>
+      <c r="AD96" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE96" s="4" t="s">
         <v>744</v>
@@ -30299,10 +30299,10 @@
         <v>1</v>
       </c>
       <c r="AI96" s="4">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="AJ96" s="4">
-        <v>7</v>
+        <v>2000</v>
       </c>
       <c r="AK96" s="4" t="b">
         <v>1</v>
@@ -30530,8 +30530,8 @@
       <c r="AC97" s="4">
         <v>36.697074000000001</v>
       </c>
-      <c r="AD97" s="4" t="b">
-        <v>1</v>
+      <c r="AD97" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE97" s="4" t="s">
         <v>743</v>
@@ -30546,10 +30546,10 @@
         <v>1</v>
       </c>
       <c r="AI97" s="4">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="AJ97" s="4">
-        <v>5</v>
+        <v>2000</v>
       </c>
       <c r="AK97" s="4" t="b">
         <v>1</v>
@@ -30777,8 +30777,8 @@
       <c r="AC98" s="4">
         <v>59.114967</v>
       </c>
-      <c r="AD98" s="4" t="b">
-        <v>1</v>
+      <c r="AD98" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE98" s="4" t="s">
         <v>744</v>
@@ -30793,10 +30793,10 @@
         <v>1</v>
       </c>
       <c r="AI98" s="4">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="AJ98" s="4">
-        <v>3</v>
+        <v>2000</v>
       </c>
       <c r="AK98" s="4" t="b">
         <v>1</v>
@@ -31024,8 +31024,8 @@
       <c r="AC99" s="4">
         <v>-54.473931</v>
       </c>
-      <c r="AD99" s="4" t="b">
-        <v>1</v>
+      <c r="AD99" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE99" s="4" t="s">
         <v>743</v>
@@ -31040,10 +31040,10 @@
         <v>1</v>
       </c>
       <c r="AI99" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AJ99" s="4">
-        <v>7</v>
+        <v>2000</v>
       </c>
       <c r="AK99" s="4" t="b">
         <v>1</v>
@@ -31271,8 +31271,8 @@
       <c r="AC100" s="4">
         <v>16.993919999999999</v>
       </c>
-      <c r="AD100" s="4" t="b">
-        <v>1</v>
+      <c r="AD100" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE100" s="4" t="s">
         <v>744</v>
@@ -31287,10 +31287,10 @@
         <v>1</v>
       </c>
       <c r="AI100" s="4">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="AJ100" s="4">
-        <v>10</v>
+        <v>2000</v>
       </c>
       <c r="AK100" s="4" t="b">
         <v>1</v>
@@ -31518,8 +31518,8 @@
       <c r="AC101" s="4">
         <v>-39.672823999999999</v>
       </c>
-      <c r="AD101" s="4" t="b">
-        <v>1</v>
+      <c r="AD101" s="4" t="s">
+        <v>1942</v>
       </c>
       <c r="AE101" s="4" t="s">
         <v>744</v>
@@ -31534,10 +31534,10 @@
         <v>1</v>
       </c>
       <c r="AI101" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AJ101" s="4">
-        <v>3</v>
+        <v>2000</v>
       </c>
       <c r="AK101" s="4" t="b">
         <v>1</v>
